--- a/data/Daily_Out_Standing.xlsx
+++ b/data/Daily_Out_Standing.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20460" windowHeight="7470" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20460" windowHeight="7470"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -23,15 +23,15 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="202" r:id="rId5"/>
-    <pivotCache cacheId="205" r:id="rId6"/>
-    <pivotCache cacheId="208" r:id="rId7"/>
-    <pivotCache cacheId="211" r:id="rId8"/>
+    <pivotCache cacheId="31" r:id="rId5"/>
+    <pivotCache cacheId="34" r:id="rId6"/>
+    <pivotCache cacheId="37" r:id="rId7"/>
+    <pivotCache cacheId="40" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{876F7934-8845-4945-9796-88D515C7AA90}">
       <x14:pivotCaches>
-        <pivotCache cacheId="201" r:id="rId9"/>
+        <pivotCache cacheId="4" r:id="rId9"/>
       </x14:pivotCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="14">
   <si>
     <t>Db id</t>
   </si>
@@ -697,7 +697,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -708,10 +711,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2465,7 +2465,7 @@
                 <a:fld id="{B8635B81-8830-4591-9F21-02E57C20B3FF}" type="VALUE">
                   <a:rPr lang="en-US"/>
                   <a:pPr>
-                    <a:defRPr sz="1500" baseline="0"/>
+                    <a:defRPr sz="1500"/>
                   </a:pPr>
                   <a:t>[VALUE]</a:t>
                 </a:fld>
@@ -2569,6 +2569,16 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-DD3E-4D04-99F9-42AACA6C5896}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="3"/>
@@ -2599,6 +2609,9 @@
                   <c15:layout/>
                   <c15:dlblFieldTable/>
                   <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-DD3E-4D04-99F9-42AACA6C5896}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3006,7 +3019,6 @@
         <c:idx val="2"/>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
@@ -3015,9 +3027,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -7556,7 +7566,123 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46160.621569560186" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46168.761142129631" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="3">
+    <cacheField name="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" numFmtId="0" hierarchy="12" level="32767"/>
+    <cacheField name="[Table1].[Outstanding].[Outstanding]" caption="Outstanding" numFmtId="0" hierarchy="3" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0" containsNumber="1" containsInteger="1" count="4">
+        <n v="113539479"/>
+        <n v="113036646"/>
+        <n v="112353157"/>
+        <n v="111353158"/>
+      </sharedItems>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{4F2E5C28-24EA-4eb8-9CBF-B6C8F9C3D259}">
+          <x15:cachedUniqueNames>
+            <x15:cachedUniqueName index="0" name="[Table1].[Outstanding].&amp;[113539479]"/>
+            <x15:cachedUniqueName index="1" name="[Table1].[Outstanding].&amp;[113036646]"/>
+            <x15:cachedUniqueName index="2" name="[Table1].[Outstanding].&amp;[112353157]"/>
+            <x15:cachedUniqueName index="3" name="[Table1].[Outstanding].&amp;[111353158]"/>
+          </x15:cachedUniqueNames>
+        </ext>
+      </extLst>
+    </cacheField>
+    <cacheField name="[Table1].[Day].[Day]" caption="Day" numFmtId="0" hierarchy="1" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-12T00:00:00" maxDate="2026-05-17T00:00:00" count="4">
+        <d v="2026-05-12T00:00:00"/>
+        <d v="2026-05-13T00:00:00"/>
+        <d v="2026-05-15T00:00:00"/>
+        <d v="2026-05-16T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="14">
+    <cacheHierarchy uniqueName="[Table1].[Db id]" caption="Db id" attribute="1" defaultMemberUniqueName="[Table1].[Db id].[All]" allUniqueName="[Table1].[Db id].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Day]" caption="Day" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Day].[All]" allUniqueName="[Table1].[Day].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Sales product]" caption="Sales product" attribute="1" defaultMemberUniqueName="[Table1].[Sales product].[All]" allUniqueName="[Table1].[Sales product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Outstanding]" caption="Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Outstanding].[All]" allUniqueName="[Table1].[Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Outstanding]" caption="Difference_Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Outstanding].[All]" allUniqueName="[Table1].[Difference_Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Rise]" caption="Difference_Rise" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Rise].[All]" allUniqueName="[Table1].[Difference_Rise].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Db id]" caption="Sum of Db id" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="0"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Day]" caption="Count of Day" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="1"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Sales product]" caption="Count of Sales product" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="2"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="3"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="4"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="5"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="2">
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Table1" uniqueName="[Table1]" caption="Table1"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Table1" caption="Table1"/>
+  </measureGroups>
+  <maps count="1">
+    <map measureGroup="0" dimension="1"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46168.761142361109" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="2">
     <cacheField name="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" numFmtId="0" hierarchy="12" level="32767"/>
@@ -7648,8 +7774,8 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46160.621570833333" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46168.761142708332" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="5">
     <cacheField name="[Table1].[Db id].[Db id]" caption="Db id" numFmtId="0" level="1">
@@ -7767,8 +7893,8 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46160.621572453703" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46168.761143171294" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="3">
     <cacheField name="[Table1].[Outstanding].[Outstanding]" caption="Outstanding" numFmtId="0" hierarchy="3" level="1">
@@ -7883,122 +8009,6 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46160.62157372685" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="3">
-    <cacheField name="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" numFmtId="0" hierarchy="12" level="32767"/>
-    <cacheField name="[Table1].[Outstanding].[Outstanding]" caption="Outstanding" numFmtId="0" hierarchy="3" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0" containsNumber="1" containsInteger="1" count="4">
-        <n v="113539479"/>
-        <n v="113036646"/>
-        <n v="112353157"/>
-        <n v="111353158"/>
-      </sharedItems>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{4F2E5C28-24EA-4eb8-9CBF-B6C8F9C3D259}">
-          <x15:cachedUniqueNames>
-            <x15:cachedUniqueName index="0" name="[Table1].[Outstanding].&amp;[113539479]"/>
-            <x15:cachedUniqueName index="1" name="[Table1].[Outstanding].&amp;[113036646]"/>
-            <x15:cachedUniqueName index="2" name="[Table1].[Outstanding].&amp;[112353157]"/>
-            <x15:cachedUniqueName index="3" name="[Table1].[Outstanding].&amp;[111353158]"/>
-          </x15:cachedUniqueNames>
-        </ext>
-      </extLst>
-    </cacheField>
-    <cacheField name="[Table1].[Day].[Day]" caption="Day" numFmtId="0" hierarchy="1" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-12T00:00:00" maxDate="2026-05-17T00:00:00" count="4">
-        <d v="2026-05-12T00:00:00"/>
-        <d v="2026-05-13T00:00:00"/>
-        <d v="2026-05-15T00:00:00"/>
-        <d v="2026-05-16T00:00:00"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="14">
-    <cacheHierarchy uniqueName="[Table1].[Db id]" caption="Db id" attribute="1" defaultMemberUniqueName="[Table1].[Db id].[All]" allUniqueName="[Table1].[Db id].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Day]" caption="Day" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Day].[All]" allUniqueName="[Table1].[Day].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Table1].[Sales product]" caption="Sales product" attribute="1" defaultMemberUniqueName="[Table1].[Sales product].[All]" allUniqueName="[Table1].[Sales product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Outstanding]" caption="Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Outstanding].[All]" allUniqueName="[Table1].[Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Table1].[Difference_Outstanding]" caption="Difference_Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Outstanding].[All]" allUniqueName="[Table1].[Difference_Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Difference_Rise]" caption="Difference_Rise" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Rise].[All]" allUniqueName="[Table1].[Difference_Rise].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Db id]" caption="Sum of Db id" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="0"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of Day]" caption="Count of Day" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="1"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of Sales product]" caption="Count of Sales product" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="2"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="3"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="4"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="5"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="2">
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Table1" uniqueName="[Table1]" caption="Table1"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Table1" caption="Table1"/>
-  </measureGroups>
-  <maps count="1">
-    <map measureGroup="0" dimension="1"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
 <file path=xl/pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46160.621568518516" backgroundQuery="1" createdVersion="3" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
   <cacheSource type="external" connectionId="1">
@@ -8071,7 +8081,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="208" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24">
   <location ref="A20:B25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
@@ -8194,7 +8204,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="211" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
   <location ref="A10:B15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField dataField="1" showAll="0"/>
@@ -8311,7 +8321,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="202" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="34" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22">
   <location ref="D10:E15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField dataField="1" showAll="0"/>
@@ -8414,7 +8424,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="205" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="37" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="A2:D7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
@@ -8551,15 +8561,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F6" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:F6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F10" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:F10"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Db id" dataDxfId="8"/>
     <tableColumn id="22" name="Day" dataDxfId="7"/>
-    <tableColumn id="3" name="Sales product" dataDxfId="3"/>
-    <tableColumn id="2" name="Outstanding" dataDxfId="1"/>
-    <tableColumn id="31" name="Difference_Outstanding" dataDxfId="2"/>
-    <tableColumn id="5" name="Difference_Rise" dataDxfId="0"/>
+    <tableColumn id="3" name="Sales product" dataDxfId="0"/>
+    <tableColumn id="2" name="Outstanding" dataDxfId="6"/>
+    <tableColumn id="31" name="Difference_Outstanding" dataDxfId="5"/>
+    <tableColumn id="5" name="Difference_Rise" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8569,11 +8579,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:C5" totalsRowShown="0">
   <autoFilter ref="A1:C5"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="ID" dataDxfId="6">
+    <tableColumn id="1" name="ID" dataDxfId="3">
       <calculatedColumnFormula>ROW()-ROW(Table1[#Headers])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" name="Day" dataDxfId="5"/>
-    <tableColumn id="3" name="Collected" dataDxfId="4"/>
+    <tableColumn id="2" name="Day" dataDxfId="2"/>
+    <tableColumn id="3" name="Collected" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8842,7 +8852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="29.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="29.7109375" style="1"/>
@@ -8975,6 +8985,50 @@
       <c r="F6" s="3">
         <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-E5)</f>
         <v>309654</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>46159</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>46163</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>46166</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>46168</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -9065,7 +9119,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
-    <col min="2" max="3" width="41.28515625" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" customWidth="1"/>
+    <col min="3" max="3" width="41.28515625" customWidth="1"/>
     <col min="4" max="4" width="31.85546875" customWidth="1"/>
     <col min="5" max="5" width="41.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -9307,11 +9362,12 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
       <x14:slicerList>
-        <x14:slicer r:id="rId2"/>
+        <x14:slicer r:id="rId3"/>
       </x14:slicerList>
     </ext>
   </extLst>

--- a/data/Daily_Out_Standing.xlsx
+++ b/data/Daily_Out_Standing.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20460" windowHeight="7470"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20460" windowHeight="7470" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -23,15 +23,15 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="178" r:id="rId5"/>
-    <pivotCache cacheId="181" r:id="rId6"/>
-    <pivotCache cacheId="184" r:id="rId7"/>
-    <pivotCache cacheId="187" r:id="rId8"/>
+    <pivotCache cacheId="1" r:id="rId5"/>
+    <pivotCache cacheId="2" r:id="rId6"/>
+    <pivotCache cacheId="3" r:id="rId7"/>
+    <pivotCache cacheId="10" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{876F7934-8845-4945-9796-88D515C7AA90}">
       <x14:pivotCaches>
-        <pivotCache cacheId="57" r:id="rId9"/>
+        <pivotCache cacheId="4" r:id="rId9"/>
       </x14:pivotCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -701,7 +701,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -712,10 +715,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1940,7 +1940,6 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1977,9 +1976,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2023,7 +2020,6 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -2060,9 +2056,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2324,7 +2318,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2478,7 +2472,6 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -2513,9 +2506,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2555,7 +2546,6 @@
         </c:spPr>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:tx>
             <c:rich>
               <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
@@ -2576,7 +2566,14 @@
                 <a:fld id="{B8635B81-8830-4591-9F21-02E57C20B3FF}" type="VALUE">
                   <a:rPr lang="en-US" b="1"/>
                   <a:pPr>
-                    <a:defRPr sz="1500"/>
+                    <a:defRPr sz="1500" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
                   </a:pPr>
                   <a:t>[VALUE]</a:t>
                 </a:fld>
@@ -2619,7 +2616,6 @@
           <c:showBubbleSize val="0"/>
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
               <c15:dlblFieldTable/>
               <c15:showDataLabelsRange val="0"/>
             </c:ext>
@@ -3173,7 +3169,6 @@
         <c:idx val="3"/>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
@@ -3182,9 +3177,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -3317,32 +3310,11 @@
           <c:symbol val="circle"/>
           <c:size val="6"/>
           <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
             <a:ln w="9525">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
@@ -7225,16 +7197,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>214312</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>71437</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>554037</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>411162</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7256,15 +7228,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>230187</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>404812</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>579437</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>150812</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7285,16 +7257,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>119062</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>1587</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>515937</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>468312</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>77787</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>277812</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>157162</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7557,8 +7529,8 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="5" name="Day 1"/>
@@ -7575,7 +7547,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -7684,125 +7656,6 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46168.866640740744" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="3">
-    <cacheField name="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" numFmtId="0" hierarchy="12" level="32767"/>
-    <cacheField name="[Table1].[Outstanding].[Outstanding]" caption="Outstanding" numFmtId="0" hierarchy="3" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0" containsNumber="1" containsInteger="1" count="4">
-        <n v="113539479"/>
-        <n v="113036646"/>
-        <n v="112353157"/>
-        <n v="111353158"/>
-      </sharedItems>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{4F2E5C28-24EA-4eb8-9CBF-B6C8F9C3D259}">
-          <x15:cachedUniqueNames>
-            <x15:cachedUniqueName index="0" name="[Table1].[Outstanding].&amp;[113539479]"/>
-            <x15:cachedUniqueName index="1" name="[Table1].[Outstanding].&amp;[113036646]"/>
-            <x15:cachedUniqueName index="2" name="[Table1].[Outstanding].&amp;[112353157]"/>
-            <x15:cachedUniqueName index="3" name="[Table1].[Outstanding].&amp;[111353158]"/>
-          </x15:cachedUniqueNames>
-        </ext>
-      </extLst>
-    </cacheField>
-    <cacheField name="[Table1].[Day].[Day]" caption="Day" numFmtId="0" hierarchy="1" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-12T00:00:00" maxDate="2026-05-27T00:00:00" count="7">
-        <d v="2026-05-12T00:00:00"/>
-        <d v="2026-05-13T00:00:00"/>
-        <d v="2026-05-15T00:00:00"/>
-        <d v="2026-05-16T00:00:00"/>
-        <d v="2026-05-21T00:00:00"/>
-        <d v="2026-05-24T00:00:00"/>
-        <d v="2026-05-26T00:00:00"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="14">
-    <cacheHierarchy uniqueName="[Table1].[Db id]" caption="Db id" attribute="1" defaultMemberUniqueName="[Table1].[Db id].[All]" allUniqueName="[Table1].[Db id].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Day]" caption="Day" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Day].[All]" allUniqueName="[Table1].[Day].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Table1].[Sales product]" caption="Sales product" attribute="1" defaultMemberUniqueName="[Table1].[Sales product].[All]" allUniqueName="[Table1].[Sales product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Outstanding]" caption="Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Outstanding].[All]" allUniqueName="[Table1].[Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Table1].[Difference_Outstanding]" caption="Difference_Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Outstanding].[All]" allUniqueName="[Table1].[Difference_Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Difference_Rise]" caption="Difference_Rise" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Rise].[All]" allUniqueName="[Table1].[Difference_Rise].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Db id]" caption="Sum of Db id" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="0"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of Day]" caption="Count of Day" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="1"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of Sales product]" caption="Count of Sales product" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="2"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="3"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="4"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="5"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="2">
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Table1" uniqueName="[Table1]" caption="Table1"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Table1" caption="Table1"/>
-  </measureGroups>
-  <maps count="1">
-    <map measureGroup="0" dimension="1"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46168.866641203706" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="2">
@@ -7898,7 +7751,7 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46168.866641550929" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="5">
@@ -8023,7 +7876,7 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46168.866641898145" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="3">
@@ -8142,6 +7995,131 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46169.609129629629" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="3">
+    <cacheField name="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" numFmtId="0" hierarchy="12" level="32767"/>
+    <cacheField name="[Table1].[Outstanding].[Outstanding]" caption="Outstanding" numFmtId="0" hierarchy="3" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0" containsNumber="1" containsInteger="1" count="7">
+        <n v="113539479"/>
+        <n v="113036646"/>
+        <n v="112353157"/>
+        <n v="111360014"/>
+        <n v="110262017"/>
+        <n v="109501260"/>
+        <n v="108785498"/>
+      </sharedItems>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{4F2E5C28-24EA-4eb8-9CBF-B6C8F9C3D259}">
+          <x15:cachedUniqueNames>
+            <x15:cachedUniqueName index="0" name="[Table1].[Outstanding].&amp;[113539479]"/>
+            <x15:cachedUniqueName index="1" name="[Table1].[Outstanding].&amp;[113036646]"/>
+            <x15:cachedUniqueName index="2" name="[Table1].[Outstanding].&amp;[112353157]"/>
+            <x15:cachedUniqueName index="3" name="[Table1].[Outstanding].&amp;[111360014]"/>
+            <x15:cachedUniqueName index="4" name="[Table1].[Outstanding].&amp;[110262017]"/>
+            <x15:cachedUniqueName index="5" name="[Table1].[Outstanding].&amp;[109501260]"/>
+            <x15:cachedUniqueName index="6" name="[Table1].[Outstanding].&amp;[108785498]"/>
+          </x15:cachedUniqueNames>
+        </ext>
+      </extLst>
+    </cacheField>
+    <cacheField name="[Table1].[Day].[Day]" caption="Day" numFmtId="0" hierarchy="1" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-12T00:00:00" maxDate="2026-05-27T00:00:00" count="7">
+        <d v="2026-05-12T00:00:00"/>
+        <d v="2026-05-13T00:00:00"/>
+        <d v="2026-05-15T00:00:00"/>
+        <d v="2026-05-16T00:00:00"/>
+        <d v="2026-05-21T00:00:00"/>
+        <d v="2026-05-24T00:00:00"/>
+        <d v="2026-05-26T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="14">
+    <cacheHierarchy uniqueName="[Table1].[Db id]" caption="Db id" attribute="1" defaultMemberUniqueName="[Table1].[Db id].[All]" allUniqueName="[Table1].[Db id].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Day]" caption="Day" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Day].[All]" allUniqueName="[Table1].[Day].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Sales product]" caption="Sales product" attribute="1" defaultMemberUniqueName="[Table1].[Sales product].[All]" allUniqueName="[Table1].[Sales product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Outstanding]" caption="Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Outstanding].[All]" allUniqueName="[Table1].[Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Outstanding]" caption="Difference_Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Outstanding].[All]" allUniqueName="[Table1].[Difference_Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Rise]" caption="Difference_Rise" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Rise].[All]" allUniqueName="[Table1].[Difference_Rise].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Db id]" caption="Sum of Db id" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="0"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Day]" caption="Count of Day" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="1"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Sales product]" caption="Count of Sales product" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="2"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="3"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="4"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="5"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="2">
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Table1" uniqueName="[Table1]" caption="Table1"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Table1" caption="Table1"/>
+  </measureGroups>
+  <maps count="1">
+    <map measureGroup="0" dimension="1"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46168.848235300924" backgroundQuery="1" createdVersion="3" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
   <cacheSource type="external" connectionId="1">
@@ -8214,16 +8192,19 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="178" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
   <location ref="A36:B44" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField dataField="1" showAll="0"/>
     <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
-      <items count="5">
+      <items count="8">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -8343,7 +8324,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="187" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24">
   <location ref="A20:B28" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
@@ -8490,7 +8471,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="181" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22">
   <location ref="D21:E29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField dataField="1" showAll="0"/>
@@ -8605,7 +8586,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="184" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="A2:D10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
@@ -8762,10 +8743,10 @@
   <tableColumns count="6">
     <tableColumn id="1" name="Db id" dataDxfId="8"/>
     <tableColumn id="22" name="Day" dataDxfId="7"/>
-    <tableColumn id="3" name="Sales product" dataDxfId="2"/>
-    <tableColumn id="2" name="Outstanding" dataDxfId="0"/>
-    <tableColumn id="31" name="Difference_Outstanding" dataDxfId="1"/>
-    <tableColumn id="5" name="Difference_Rise" dataDxfId="6"/>
+    <tableColumn id="3" name="Sales product" dataDxfId="6"/>
+    <tableColumn id="2" name="Outstanding" dataDxfId="5"/>
+    <tableColumn id="31" name="Difference_Outstanding" dataDxfId="4"/>
+    <tableColumn id="5" name="Difference_Rise" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8775,11 +8756,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:C5" totalsRowShown="0">
   <autoFilter ref="A1:C5"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="ID" dataDxfId="5">
+    <tableColumn id="1" name="ID" dataDxfId="2">
       <calculatedColumnFormula>ROW()-ROW(Table1[#Headers])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" name="Day" dataDxfId="4"/>
-    <tableColumn id="3" name="Collected" dataDxfId="3"/>
+    <tableColumn id="2" name="Day" dataDxfId="1"/>
+    <tableColumn id="3" name="Collected" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9337,8 +9318,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
-    <col min="2" max="2" width="31.85546875" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" customWidth="1"/>
+    <col min="2" max="3" width="41.28515625" customWidth="1"/>
     <col min="4" max="4" width="31.85546875" customWidth="1"/>
     <col min="5" max="5" width="41.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>

--- a/data/Daily_Out_Standing.xlsx
+++ b/data/Daily_Out_Standing.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20460" windowHeight="7470" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20460" windowHeight="7470" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -23,15 +23,15 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId5"/>
-    <pivotCache cacheId="2" r:id="rId6"/>
-    <pivotCache cacheId="3" r:id="rId7"/>
-    <pivotCache cacheId="10" r:id="rId8"/>
+    <pivotCache cacheId="80" r:id="rId5"/>
+    <pivotCache cacheId="83" r:id="rId6"/>
+    <pivotCache cacheId="86" r:id="rId7"/>
+    <pivotCache cacheId="89" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{876F7934-8845-4945-9796-88D515C7AA90}">
       <x14:pivotCaches>
-        <pivotCache cacheId="4" r:id="rId9"/>
+        <pivotCache cacheId="7" r:id="rId9"/>
       </x14:pivotCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="14">
   <si>
     <t>Db id</t>
   </si>
@@ -125,7 +125,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="6" formatCode="&quot;MK&quot;#,##0;[Red]\-&quot;MK&quot;#,##0"/>
     <numFmt numFmtId="8" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
@@ -617,7 +618,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -637,9 +638,6 @@
     <xf numFmtId="8" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -650,6 +648,24 @@
     </xf>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -698,33 +714,33 @@
   <dxfs count="11">
     <dxf>
       <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="12" formatCode="&quot;MK&quot;#,##0.00;[Red]\-&quot;MK&quot;#,##0.00"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -845,9 +861,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>PIVOT!$D$22:$D$29</c:f>
+              <c:f>PIVOT!$D$22:$D$32</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>12/05/2026</c:v>
                 </c:pt>
@@ -868,16 +884,25 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>26/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>27/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>28/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30/05/2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PIVOT!$E$22:$E$29</c:f>
+              <c:f>PIVOT!$E$22:$E$32</c:f>
               <c:numCache>
                 <c:formatCode>"MK"#,##0.00_);[Red]\("MK"#,##0.00\)</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -898,6 +923,15 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>715762</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>396800</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>326006</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>623821</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1219,9 +1253,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>PIVOT!$A$37:$A$44</c:f>
+              <c:f>PIVOT!$A$37:$A$47</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>12/05/2026</c:v>
                 </c:pt>
@@ -1242,16 +1276,25 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>26/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>27/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>28/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30/05/2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PIVOT!$B$37:$B$44</c:f>
+              <c:f>PIVOT!$B$37:$B$47</c:f>
               <c:numCache>
                 <c:formatCode>"MK"#,##0.00_);[Red]\("MK"#,##0.00\)</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1272,6 +1315,15 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>715762</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>396800</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>326006</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>623821</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1595,9 +1647,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>PIVOT!$A$21:$A$28</c:f>
+              <c:f>PIVOT!$A$21:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>12/05/2026</c:v>
                 </c:pt>
@@ -1618,16 +1670,25 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>26/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>27/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>28/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30/05/2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PIVOT!$B$21:$B$28</c:f>
+              <c:f>PIVOT!$B$21:$B$31</c:f>
               <c:numCache>
                 <c:formatCode>"MK"#,##0.00_);[Red]\("MK"#,##0.00\)</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1648,6 +1709,15 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>-44995</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-318962</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-70794</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>297815</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2099,6 +2169,45 @@
           <c:symbol val="none"/>
         </c:marker>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:gradFill flip="none" rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1"/>
+              </a:gs>
+              <a:gs pos="75000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="51000">
+                <a:schemeClr val="accent1">
+                  <a:alpha val="75000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="20000"/>
+                  <a:lumOff val="80000"/>
+                  <a:alpha val="15000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="10800000" scaled="1"/>
+            <a:tileRect/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout>
@@ -2166,9 +2275,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>PIVOT!$D$22:$D$29</c:f>
+              <c:f>PIVOT!$D$22:$D$32</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>12/05/2026</c:v>
                 </c:pt>
@@ -2189,16 +2298,25 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>26/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>27/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>28/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30/05/2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PIVOT!$E$22:$E$29</c:f>
+              <c:f>PIVOT!$E$22:$E$32</c:f>
               <c:numCache>
                 <c:formatCode>"MK"#,##0.00_);[Red]\("MK"#,##0.00\)</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2219,6 +2337,15 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>715762</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>396800</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>326006</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>623821</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2318,7 +2445,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2624,38 +2751,6 @@
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="6"/>
-        <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent2">
-                  <a:satMod val="103000"/>
-                  <a:lumMod val="102000"/>
-                  <a:tint val="94000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="50000">
-                <a:schemeClr val="accent2">
-                  <a:satMod val="110000"/>
-                  <a:lumMod val="100000"/>
-                  <a:shade val="100000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="99000"/>
-                  <a:satMod val="120000"/>
-                  <a:shade val="78000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="7"/>
@@ -2739,7 +2834,17 @@
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.12859806994677986"/>
+          <c:y val="0.12316868690168915"/>
+          <c:w val="0.84946705375102571"/>
+          <c:h val="0.64077106544254581"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -2848,9 +2953,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PIVOT!$A$37:$A$44</c:f>
+              <c:f>PIVOT!$A$37:$A$47</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>12/05/2026</c:v>
                 </c:pt>
@@ -2871,16 +2976,25 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>26/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>27/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>28/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30/05/2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PIVOT!$B$37:$B$44</c:f>
+              <c:f>PIVOT!$B$37:$B$47</c:f>
               <c:numCache>
                 <c:formatCode>"MK"#,##0.00_);[Red]\("MK"#,##0.00\)</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2901,6 +3015,15 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>715762</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>396800</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>326006</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>623821</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2998,7 +3121,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx2"/>
                 </a:solidFill>
@@ -3333,7 +3456,17 @@
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="6.4007253347866916E-2"/>
+          <c:y val="4.0921432053601825E-2"/>
+          <c:w val="0.93599274665213306"/>
+          <c:h val="0.91419127483660245"/>
+        </c:manualLayout>
+      </c:layout>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -3505,9 +3638,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>PIVOT!$A$21:$A$28</c:f>
+              <c:f>PIVOT!$A$21:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>12/05/2026</c:v>
                 </c:pt>
@@ -3528,16 +3661,25 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>26/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>27/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>28/05/2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30/05/2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PIVOT!$B$21:$B$28</c:f>
+              <c:f>PIVOT!$B$21:$B$31</c:f>
               <c:numCache>
                 <c:formatCode>"MK"#,##0.00_);[Red]\("MK"#,##0.00\)</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3558,6 +3700,15 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>-44995</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-318962</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-70794</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>297815</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3679,20 +3830,6 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="&quot;MK&quot;#,##0.00_);[Red]\(&quot;MK&quot;#,##0.00\)" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -3736,7 +3873,7 @@
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
+        <a:ln w="25400">
           <a:noFill/>
         </a:ln>
         <a:effectLst/>
@@ -7293,15 +7430,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>253999</xdr:colOff>
+      <xdr:colOff>253998</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>142874</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>126999</xdr:rowOff>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>-1</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7310,8 +7447,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="253999" y="1381125"/>
-          <a:ext cx="21605875" cy="7699374"/>
+          <a:off x="253998" y="1381125"/>
+          <a:ext cx="31940501" cy="10501312"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -7359,14 +7496,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>9074</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7375,8 +7512,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1254125" y="2505075"/>
-          <a:ext cx="2422525" cy="2038350"/>
+          <a:off x="1285875" y="2095500"/>
+          <a:ext cx="2476500" cy="4009574"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7416,7 +7553,15 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100"/>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:effectLst>
+              <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                <a:prstClr val="black">
+                  <a:alpha val="40000"/>
+                </a:prstClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -7425,15 +7570,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>301625</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>31751</xdr:rowOff>
+      <xdr:colOff>476251</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>23813</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>19051</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>523876</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7456,16 +7601,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>160613</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>142927</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>-1</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>238124</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>595313</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>23813</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7474,8 +7619,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="763863" y="4714927"/>
-          <a:ext cx="10332761" cy="3857573"/>
+          <a:off x="1238249" y="6477000"/>
+          <a:ext cx="11739564" cy="4786313"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -7519,18 +7664,18 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>368300</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:colOff>261937</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>119063</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>355600</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>384562</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>119063</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="5" name="Day 1"/>
@@ -7547,7 +7692,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -7557,8 +7702,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1574800" y="2619375"/>
-              <a:ext cx="1797050" cy="1790700"/>
+              <a:off x="1500187" y="2405063"/>
+              <a:ext cx="1980000" cy="3429000"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7591,15 +7736,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>206374</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>183285</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>174625</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>107950</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7622,16 +7767,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>158749</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>-1</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>63500</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>142874</xdr:rowOff>
+      <xdr:col>50</xdr:col>
+      <xdr:colOff>-1</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>47626</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7656,12 +7801,36 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46168.866641203706" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46174.465531712965" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
   <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="2">
+  <cacheFields count="3">
     <cacheField name="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" numFmtId="0" hierarchy="12" level="32767"/>
+    <cacheField name="[Table1].[Outstanding].[Outstanding]" caption="Outstanding" numFmtId="0" hierarchy="3" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0" containsNumber="1" containsInteger="1" count="7">
+        <n v="113539479"/>
+        <n v="113036646"/>
+        <n v="112353157"/>
+        <n v="111360014"/>
+        <n v="110262017"/>
+        <n v="109501260"/>
+        <n v="108785498"/>
+      </sharedItems>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{4F2E5C28-24EA-4eb8-9CBF-B6C8F9C3D259}">
+          <x15:cachedUniqueNames>
+            <x15:cachedUniqueName index="0" name="[Table1].[Outstanding].&amp;[113539479]"/>
+            <x15:cachedUniqueName index="1" name="[Table1].[Outstanding].&amp;[113036646]"/>
+            <x15:cachedUniqueName index="2" name="[Table1].[Outstanding].&amp;[112353157]"/>
+            <x15:cachedUniqueName index="3" name="[Table1].[Outstanding].&amp;[111360014]"/>
+            <x15:cachedUniqueName index="4" name="[Table1].[Outstanding].&amp;[110262017]"/>
+            <x15:cachedUniqueName index="5" name="[Table1].[Outstanding].&amp;[109501260]"/>
+            <x15:cachedUniqueName index="6" name="[Table1].[Outstanding].&amp;[108785498]"/>
+          </x15:cachedUniqueNames>
+        </ext>
+      </extLst>
+    </cacheField>
     <cacheField name="[Table1].[Day].[Day]" caption="Day" numFmtId="0" hierarchy="1" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-12T00:00:00" maxDate="2026-05-27T00:00:00" count="7">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-12T00:00:00" maxDate="2026-05-31T00:00:00" count="10">
         <d v="2026-05-12T00:00:00"/>
         <d v="2026-05-13T00:00:00"/>
         <d v="2026-05-15T00:00:00"/>
@@ -7669,6 +7838,113 @@
         <d v="2026-05-21T00:00:00"/>
         <d v="2026-05-24T00:00:00"/>
         <d v="2026-05-26T00:00:00"/>
+        <d v="2026-05-27T00:00:00"/>
+        <d v="2026-05-28T00:00:00"/>
+        <d v="2026-05-30T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="14">
+    <cacheHierarchy uniqueName="[Table1].[Db id]" caption="Db id" attribute="1" defaultMemberUniqueName="[Table1].[Db id].[All]" allUniqueName="[Table1].[Db id].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Day]" caption="Day" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Day].[All]" allUniqueName="[Table1].[Day].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Sales product]" caption="Sales product" attribute="1" defaultMemberUniqueName="[Table1].[Sales product].[All]" allUniqueName="[Table1].[Sales product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Outstanding]" caption="Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Outstanding].[All]" allUniqueName="[Table1].[Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Outstanding]" caption="Difference_Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Outstanding].[All]" allUniqueName="[Table1].[Difference_Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Difference_Rise]" caption="Difference_Rise" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Rise].[All]" allUniqueName="[Table1].[Difference_Rise].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Db id]" caption="Sum of Db id" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="0"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Day]" caption="Count of Day" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="1"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Sales product]" caption="Count of Sales product" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="2"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="3"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="4"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="5"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="2">
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Table1" uniqueName="[Table1]" caption="Table1"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Table1" caption="Table1"/>
+  </measureGroups>
+  <maps count="1">
+    <map measureGroup="0" dimension="1"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46174.465532175927" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="2">
+    <cacheField name="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" numFmtId="0" hierarchy="12" level="32767"/>
+    <cacheField name="[Table1].[Day].[Day]" caption="Day" numFmtId="0" hierarchy="1" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-12T00:00:00" maxDate="2026-05-31T00:00:00" count="10">
+        <d v="2026-05-12T00:00:00"/>
+        <d v="2026-05-13T00:00:00"/>
+        <d v="2026-05-15T00:00:00"/>
+        <d v="2026-05-16T00:00:00"/>
+        <d v="2026-05-21T00:00:00"/>
+        <d v="2026-05-24T00:00:00"/>
+        <d v="2026-05-26T00:00:00"/>
+        <d v="2026-05-27T00:00:00"/>
+        <d v="2026-05-28T00:00:00"/>
+        <d v="2026-05-30T00:00:00"/>
       </sharedItems>
     </cacheField>
   </cacheFields>
@@ -7751,12 +8027,12 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46168.866641550929" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46174.465532523151" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="5">
     <cacheField name="[Table1].[Db id].[Db id]" caption="Db id" numFmtId="0" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="9" count="7">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="12" count="10">
         <n v="1"/>
         <n v="2"/>
         <n v="4"/>
@@ -7764,6 +8040,9 @@
         <n v="6"/>
         <n v="8"/>
         <n v="9"/>
+        <n v="10"/>
+        <n v="11"/>
+        <n v="12"/>
       </sharedItems>
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{4F2E5C28-24EA-4eb8-9CBF-B6C8F9C3D259}">
@@ -7775,6 +8054,9 @@
             <x15:cachedUniqueName index="4" name="[Table1].[Db id].&amp;[6]"/>
             <x15:cachedUniqueName index="5" name="[Table1].[Db id].&amp;[8]"/>
             <x15:cachedUniqueName index="6" name="[Table1].[Db id].&amp;[9]"/>
+            <x15:cachedUniqueName index="7" name="[Table1].[Db id].&amp;[10]"/>
+            <x15:cachedUniqueName index="8" name="[Table1].[Db id].&amp;[11]"/>
+            <x15:cachedUniqueName index="9" name="[Table1].[Db id].&amp;[12]"/>
           </x15:cachedUniqueNames>
         </ext>
       </extLst>
@@ -7876,8 +8158,8 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46168.866641898145" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46174.465532986113" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="3">
     <cacheField name="[Table1].[Outstanding].[Outstanding]" caption="Outstanding" numFmtId="0" hierarchy="3" level="1">
@@ -7899,7 +8181,7 @@
       </extLst>
     </cacheField>
     <cacheField name="[Table1].[Day].[Day]" caption="Day" numFmtId="0" hierarchy="1" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-12T00:00:00" maxDate="2026-05-27T00:00:00" count="7">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-12T00:00:00" maxDate="2026-05-31T00:00:00" count="10">
         <d v="2026-05-12T00:00:00"/>
         <d v="2026-05-13T00:00:00"/>
         <d v="2026-05-15T00:00:00"/>
@@ -7907,6 +8189,9 @@
         <d v="2026-05-21T00:00:00"/>
         <d v="2026-05-24T00:00:00"/>
         <d v="2026-05-26T00:00:00"/>
+        <d v="2026-05-27T00:00:00"/>
+        <d v="2026-05-28T00:00:00"/>
+        <d v="2026-05-30T00:00:00"/>
       </sharedItems>
     </cacheField>
     <cacheField name="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" numFmtId="0" hierarchy="13" level="32767"/>
@@ -7995,133 +8280,8 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46169.609129629629" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="3">
-    <cacheField name="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" numFmtId="0" hierarchy="12" level="32767"/>
-    <cacheField name="[Table1].[Outstanding].[Outstanding]" caption="Outstanding" numFmtId="0" hierarchy="3" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0" containsNumber="1" containsInteger="1" count="7">
-        <n v="113539479"/>
-        <n v="113036646"/>
-        <n v="112353157"/>
-        <n v="111360014"/>
-        <n v="110262017"/>
-        <n v="109501260"/>
-        <n v="108785498"/>
-      </sharedItems>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{4F2E5C28-24EA-4eb8-9CBF-B6C8F9C3D259}">
-          <x15:cachedUniqueNames>
-            <x15:cachedUniqueName index="0" name="[Table1].[Outstanding].&amp;[113539479]"/>
-            <x15:cachedUniqueName index="1" name="[Table1].[Outstanding].&amp;[113036646]"/>
-            <x15:cachedUniqueName index="2" name="[Table1].[Outstanding].&amp;[112353157]"/>
-            <x15:cachedUniqueName index="3" name="[Table1].[Outstanding].&amp;[111360014]"/>
-            <x15:cachedUniqueName index="4" name="[Table1].[Outstanding].&amp;[110262017]"/>
-            <x15:cachedUniqueName index="5" name="[Table1].[Outstanding].&amp;[109501260]"/>
-            <x15:cachedUniqueName index="6" name="[Table1].[Outstanding].&amp;[108785498]"/>
-          </x15:cachedUniqueNames>
-        </ext>
-      </extLst>
-    </cacheField>
-    <cacheField name="[Table1].[Day].[Day]" caption="Day" numFmtId="0" hierarchy="1" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-05-12T00:00:00" maxDate="2026-05-27T00:00:00" count="7">
-        <d v="2026-05-12T00:00:00"/>
-        <d v="2026-05-13T00:00:00"/>
-        <d v="2026-05-15T00:00:00"/>
-        <d v="2026-05-16T00:00:00"/>
-        <d v="2026-05-21T00:00:00"/>
-        <d v="2026-05-24T00:00:00"/>
-        <d v="2026-05-26T00:00:00"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="14">
-    <cacheHierarchy uniqueName="[Table1].[Db id]" caption="Db id" attribute="1" defaultMemberUniqueName="[Table1].[Db id].[All]" allUniqueName="[Table1].[Db id].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Day]" caption="Day" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Day].[All]" allUniqueName="[Table1].[Day].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Table1].[Sales product]" caption="Sales product" attribute="1" defaultMemberUniqueName="[Table1].[Sales product].[All]" allUniqueName="[Table1].[Sales product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Outstanding]" caption="Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Outstanding].[All]" allUniqueName="[Table1].[Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Table1].[Difference_Outstanding]" caption="Difference_Outstanding" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Outstanding].[All]" allUniqueName="[Table1].[Difference_Outstanding].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Difference_Rise]" caption="Difference_Rise" attribute="1" defaultMemberUniqueName="[Table1].[Difference_Rise].[All]" allUniqueName="[Table1].[Difference_Rise].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Db id]" caption="Sum of Db id" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="0"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of Day]" caption="Count of Day" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="1"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of Sales product]" caption="Count of Sales product" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="2"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Outstanding]" caption="Sum of Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="3"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Outstanding]" caption="Sum of Difference_Outstanding" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="4"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Difference_Rise]" caption="Sum of Difference_Rise" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="5"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="2">
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Table1" uniqueName="[Table1]" caption="Table1"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Table1" caption="Table1"/>
-  </measureGroups>
-  <maps count="1">
-    <map measureGroup="0" dimension="1"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
 <file path=xl/pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46168.848235300924" backgroundQuery="1" createdVersion="3" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="Bright paipila" refreshedDate="46174.462236226849" backgroundQuery="1" createdVersion="3" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
   <cacheSource type="external" connectionId="1">
     <extLst>
       <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{F057638F-6D5F-4e77-A914-E7F072B9BCA8}">
@@ -8185,31 +8345,27 @@
   <kpis count="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition slicerData="1" pivotCacheId="10" supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+      <x14:pivotCacheDefinition slicerData="1" pivotCacheId="11" supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
-  <location ref="A36:B44" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="89" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="27">
+  <location ref="A20:B31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
-    <pivotField dataField="1" showAll="0"/>
     <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
-      <items count="8">
+      <items count="5">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1">
-      <items count="8">
+      <items count="11">
         <item x="0" e="0"/>
         <item x="1" e="0"/>
         <item x="2" e="0"/>
@@ -8217,15 +8373,19 @@
         <item x="4" e="0"/>
         <item x="5" e="0"/>
         <item x="6" e="0"/>
+        <item x="7" e="0"/>
+        <item x="8" e="0"/>
+        <item x="9" e="0"/>
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField dataField="1" showAll="0"/>
   </pivotFields>
   <rowFields count="2">
-    <field x="2"/>
     <field x="1"/>
+    <field x="0"/>
   </rowFields>
-  <rowItems count="8">
+  <rowItems count="11">
     <i>
       <x/>
     </i>
@@ -8247,6 +8407,15 @@
     <i>
       <x v="6"/>
     </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
@@ -8255,10 +8424,10 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Difference_Outstanding" fld="0" baseField="0" baseItem="0" numFmtId="8"/>
+    <dataField name="Sum of Difference_Rise" fld="2" baseField="0" baseItem="0" numFmtId="8"/>
   </dataFields>
   <chartFormats count="3">
-    <chartFormat chart="13" format="0" series="1">
+    <chartFormat chart="20" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -8267,19 +8436,16 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="16" format="6">
+    <chartFormat chart="21" format="1" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
+        <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="3"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="16" format="7" series="1">
+    <chartFormat chart="22" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -8324,37 +8490,30 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="24">
-  <location ref="A20:B28" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="83" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22">
+  <location ref="D21:E32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField dataField="1" showAll="0"/>
     <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
-      <items count="5">
+      <items count="11">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1">
-      <items count="8">
-        <item x="0" e="0"/>
-        <item x="1" e="0"/>
-        <item x="2" e="0"/>
-        <item x="3" e="0"/>
-        <item x="4" e="0"/>
-        <item x="5" e="0"/>
-        <item x="6" e="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
   </pivotFields>
-  <rowFields count="2">
+  <rowFields count="1">
     <field x="1"/>
-    <field x="0"/>
   </rowFields>
-  <rowItems count="8">
+  <rowItems count="11">
     <i>
       <x/>
     </i>
@@ -8376,142 +8535,14 @@
     <i>
       <x v="6"/>
     </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Difference_Rise" fld="2" baseField="0" baseItem="0" numFmtId="8"/>
-  </dataFields>
-  <chartFormats count="5">
-    <chartFormat chart="20" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="21" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="22" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="23" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="23" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="14">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="2">
-    <rowHierarchyUsage hierarchyUsage="1"/>
-    <rowHierarchyUsage hierarchyUsage="3"/>
-  </rowHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_Daily_Out_Standing.xlsx!Table1">
-        <x15:activeTabTopLevelEntity name="[Table1]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22">
-  <location ref="D21:E29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
-      <items count="8">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="8">
     <i>
-      <x/>
+      <x v="7"/>
     </i>
     <i>
-      <x v="1"/>
+      <x v="8"/>
     </i>
     <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
+      <x v="9"/>
     </i>
     <i t="grand">
       <x/>
@@ -8542,7 +8573,7 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="18" format="5" series="1">
+    <chartFormat chart="18" format="6" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -8585,12 +8616,12 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
-  <location ref="A2:D10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="86" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+  <location ref="A2:D13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
-      <items count="8">
+      <items count="11">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -8598,6 +8629,9 @@
         <item x="4"/>
         <item x="5"/>
         <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -8609,7 +8643,7 @@
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="8">
+  <rowItems count="11">
     <i>
       <x/>
     </i>
@@ -8630,6 +8664,15 @@
     </i>
     <i>
       <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
     </i>
     <i t="grand">
       <x/>
@@ -8690,6 +8733,147 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="80" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19">
+  <location ref="A36:B47" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
+      <items count="8">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1">
+      <items count="11">
+        <item x="0" e="0"/>
+        <item x="1" e="0"/>
+        <item x="2" e="0"/>
+        <item x="3" e="0"/>
+        <item x="4" e="0"/>
+        <item x="5" e="0"/>
+        <item x="6" e="0"/>
+        <item x="7" e="0"/>
+        <item x="8" e="0"/>
+        <item x="9" e="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="2"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Difference_Outstanding" fld="0" baseField="0" baseItem="0" numFmtId="8"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="13" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="18" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="14">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="2">
+    <rowHierarchyUsage hierarchyUsage="1"/>
+    <rowHierarchyUsage hierarchyUsage="3"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_Daily_Out_Standing.xlsx!Table1">
+        <x15:activeTabTopLevelEntity name="[Table1]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="Slicer_Day" sourceName="[Table1].[Day]">
   <pivotTables>
@@ -8699,10 +8883,10 @@
     <pivotTable tabId="3" name="PivotTable1"/>
   </pivotTables>
   <data>
-    <olap pivotCacheId="10">
+    <olap pivotCacheId="11">
       <levels count="2">
         <level uniqueName="[Table1].[Day].[(All)]" sourceCaption="(All)" count="0"/>
-        <level uniqueName="[Table1].[Day].[Day]" sourceCaption="Day" count="8">
+        <level uniqueName="[Table1].[Day].[Day]" sourceCaption="Day" count="12">
           <ranges>
             <range startItem="0">
               <i n="[Table1].[Day].&amp;[2026-05-12T00:00:00]" c="12/05/2026"/>
@@ -8712,6 +8896,10 @@
               <i n="[Table1].[Day].&amp;[2026-05-21T00:00:00]" c="21/05/2026"/>
               <i n="[Table1].[Day].&amp;[2026-05-24T00:00:00]" c="24/05/2026"/>
               <i n="[Table1].[Day].&amp;[2026-05-26T00:00:00]" c="26/05/2026"/>
+              <i n="[Table1].[Day].&amp;[2026-05-27T00:00:00]" c="27/05/2026"/>
+              <i n="[Table1].[Day].&amp;[2026-05-28T00:00:00]" c="28/05/2026"/>
+              <i n="[Table1].[Day].&amp;[2026-05-30T00:00:00]" c="30/05/2026"/>
+              <i n="[Table1].[Day].&amp;" c="(blank)" nd="1"/>
               <i n="[Table1].[Day].&amp;[2026-05-14T00:00:00]" c="14/05/2026" nd="1"/>
             </range>
           </ranges>
@@ -8733,20 +8921,20 @@
 
 <file path=xl/slicers/slicer2.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <slicer name="Day 1" cache="Slicer_Day" caption="Day" level="1" style="SlicerStyleDark5" rowHeight="241300"/>
+  <slicer name="Day 1" cache="Slicer_Day" caption="Day" level="1" style="SlicerStyleDark5" rowHeight="216000"/>
 </slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F9" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:F9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F16" totalsRowShown="0" headerRowDxfId="10" dataDxfId="1">
+  <autoFilter ref="A1:F16"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Db id" dataDxfId="8"/>
-    <tableColumn id="22" name="Day" dataDxfId="7"/>
-    <tableColumn id="3" name="Sales product" dataDxfId="6"/>
-    <tableColumn id="2" name="Outstanding" dataDxfId="5"/>
-    <tableColumn id="31" name="Difference_Outstanding" dataDxfId="4"/>
-    <tableColumn id="5" name="Difference_Rise" dataDxfId="3"/>
+    <tableColumn id="1" name="Db id" dataDxfId="6"/>
+    <tableColumn id="22" name="Day" dataDxfId="5"/>
+    <tableColumn id="3" name="Sales product" dataDxfId="4"/>
+    <tableColumn id="2" name="Outstanding" dataDxfId="3"/>
+    <tableColumn id="31" name="Difference_Outstanding" dataDxfId="0"/>
+    <tableColumn id="5" name="Difference_Rise" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8756,11 +8944,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:C5" totalsRowShown="0">
   <autoFilter ref="A1:C5"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="ID" dataDxfId="2">
+    <tableColumn id="1" name="ID" dataDxfId="9">
       <calculatedColumnFormula>ROW()-ROW(Table1[#Headers])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" name="Day" dataDxfId="1"/>
-    <tableColumn id="3" name="Collected" dataDxfId="0"/>
+    <tableColumn id="2" name="Day" dataDxfId="8"/>
+    <tableColumn id="3" name="Collected" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9029,7 +9217,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultColWidth="29.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="29.7109375" style="1"/>
@@ -9059,176 +9247,274 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+      <c r="A2" s="9">
         <f>ROW()-ROW(Table1[#Headers])</f>
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="10">
         <v>46154</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="13">
         <v>113539479</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="13">
         <f ca="1">IFERROR(OFFSET(Table1[[#This Row],[Outstanding]],-1,0) - Table1[[#This Row],[Outstanding]], 0)</f>
         <v>0</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="13">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+      <c r="A3" s="9">
         <f>ROW()-ROW(Table1[#Headers])</f>
         <v>2</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="10">
         <v>46155</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="13">
         <v>113036646</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="13">
         <f ca="1">IFERROR(OFFSET(Table1[[#This Row],[Outstanding]],-1,0) - Table1[[#This Row],[Outstanding]], 0)</f>
         <v>502833</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="13">
         <f ca="1">SUM(Table1[[#This Row],[Difference_Outstanding]]-E2)</f>
         <v>502833</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="A4" s="14">
         <f>ROW()-ROW(Table1[#Headers])</f>
         <v>3</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="15">
         <v>46156</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="A5" s="9">
         <f>ROW()-ROW(Table1[#Headers])</f>
         <v>4</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="10">
         <v>46157</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="17">
         <v>112353157</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="13">
         <f>SUM(D3-Table1[[#This Row],[Outstanding]])</f>
         <v>683489</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="13">
         <f ca="1">SUM(Table1[[#This Row],[Difference_Outstanding]]-E3)</f>
         <v>180656</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="A6" s="9">
         <f>ROW()-ROW(Table1[#Headers])</f>
         <v>5</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="10">
         <v>46158</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="17">
         <v>111360014</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="13">
         <f>SUM(D5-Table1[[#This Row],[Outstanding]])</f>
         <v>993143</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="13">
         <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-E5)</f>
         <v>309654</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="10">
         <v>46163</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="17">
         <v>110262017</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="13">
         <f>SUM(D6-Table1[[#This Row],[Outstanding]])</f>
         <v>1097997</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="13">
         <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-E6)</f>
         <v>104854</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="A8" s="9">
         <v>8</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="10">
         <v>46166</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="13">
         <v>109501260</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="13">
         <f>SUM(D7-Table1[[#This Row],[Outstanding]])</f>
         <v>760757</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="13">
         <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-E7)</f>
         <v>-337240</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="A9" s="9">
         <v>9</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="10">
         <v>46168</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="17">
         <v>108785498</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="13">
         <f>SUM(D8-Table1[[#This Row],[Outstanding]])</f>
         <v>715762</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="13">
         <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-E8)</f>
         <v>-44995</v>
       </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <v>10</v>
+      </c>
+      <c r="B10" s="10">
+        <v>46169</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="18">
+        <v>108388698</v>
+      </c>
+      <c r="E10" s="13">
+        <f>SUM(D9-Table1[[#This Row],[Outstanding]])</f>
+        <v>396800</v>
+      </c>
+      <c r="F10" s="13">
+        <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-E9)</f>
+        <v>-318962</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="9">
+        <v>11</v>
+      </c>
+      <c r="B11" s="10">
+        <v>46170</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="18">
+        <v>108062692</v>
+      </c>
+      <c r="E11" s="13">
+        <f>SUM(D10-Table1[[#This Row],[Outstanding]])</f>
+        <v>326006</v>
+      </c>
+      <c r="F11" s="13">
+        <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-E10)</f>
+        <v>-70794</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
+        <v>12</v>
+      </c>
+      <c r="B12" s="10">
+        <v>46172</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="18">
+        <v>107438871</v>
+      </c>
+      <c r="E12" s="13">
+        <f>SUM(D11-Table1[[#This Row],[Outstanding]])</f>
+        <v>623821</v>
+      </c>
+      <c r="F12" s="13">
+        <f>SUM(Table1[[#This Row],[Difference_Outstanding]]-E11)</f>
+        <v>297815</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9314,11 +9600,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:E44"/>
+  <dimension ref="A2:E47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
-    <col min="2" max="3" width="41.28515625" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" customWidth="1"/>
+    <col min="3" max="3" width="41.28515625" customWidth="1"/>
     <col min="4" max="4" width="31.85546875" customWidth="1"/>
     <col min="5" max="5" width="41.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -9326,7 +9613,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
@@ -9340,119 +9627,161 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
+      <c r="A3" s="9">
         <v>1</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="7">
         <v>113539479</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="7">
         <v>0</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="10">
+      <c r="A4" s="9">
         <v>2</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <v>113036646</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="7">
         <v>502833</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <v>502833</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
+      <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>112353157</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <v>683489</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <v>180656</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
+      <c r="A6" s="9">
         <v>5</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <v>111360014</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>993143</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <v>309654</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
+      <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="7">
         <v>110262017</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <v>1097997</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <v>104854</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
+      <c r="A8" s="9">
         <v>8</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="7">
         <v>109501260</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>760757</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>-337240</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+      <c r="A9" s="9">
         <v>9</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="7">
         <v>108785498</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>715762</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <v>-44995</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="9">
+        <v>10</v>
+      </c>
+      <c r="B10" s="7">
+        <v>108388698</v>
+      </c>
+      <c r="C10" s="7">
+        <v>396800</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-318962</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="9">
+        <v>11</v>
+      </c>
+      <c r="B11" s="7">
+        <v>108062692</v>
+      </c>
+      <c r="C11" s="7">
+        <v>326006</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-70794</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
+        <v>12</v>
+      </c>
+      <c r="B12" s="7">
+        <v>107438871</v>
+      </c>
+      <c r="C12" s="7">
+        <v>623821</v>
+      </c>
+      <c r="D12" s="7">
+        <v>297815</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="8">
-        <v>778838071</v>
-      </c>
-      <c r="C10" s="8">
-        <v>4753981</v>
-      </c>
-      <c r="D10" s="8">
-        <v>715762</v>
+      <c r="B13" s="7">
+        <v>1102728332</v>
+      </c>
+      <c r="C13" s="7">
+        <v>6100608</v>
+      </c>
+      <c r="D13" s="7">
+        <v>623821</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B20" t="s">
@@ -9460,13 +9789,13 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="11">
+      <c r="A21" s="10">
         <v>46154</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="11">
         <v>0</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E21" t="s">
@@ -9474,113 +9803,155 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="11">
+      <c r="A22" s="10">
         <v>46155</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="11">
         <v>502833</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="10">
         <v>46154</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="11">
+      <c r="A23" s="10">
         <v>46157</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="11">
         <v>180656</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="10">
         <v>46155</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="11">
         <v>502833</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="11">
+      <c r="A24" s="10">
         <v>46158</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="11">
         <v>309654</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="10">
         <v>46157</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="11">
         <v>683489</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="11">
+      <c r="A25" s="10">
         <v>46163</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="11">
         <v>104854</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="10">
         <v>46158</v>
       </c>
-      <c r="E25" s="12">
+      <c r="E25" s="11">
         <v>993143</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="11">
+      <c r="A26" s="10">
         <v>46166</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="11">
         <v>-337240</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="10">
         <v>46163</v>
       </c>
-      <c r="E26" s="12">
+      <c r="E26" s="11">
         <v>1097997</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="11">
+      <c r="A27" s="10">
         <v>46168</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="11">
         <v>-44995</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="10">
         <v>46166</v>
       </c>
-      <c r="E27" s="12">
+      <c r="E27" s="11">
         <v>760757</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" s="12">
-        <v>715762</v>
-      </c>
-      <c r="D28" s="11">
+      <c r="A28" s="10">
+        <v>46169</v>
+      </c>
+      <c r="B28" s="11">
+        <v>-318962</v>
+      </c>
+      <c r="D28" s="10">
         <v>46168</v>
       </c>
-      <c r="E28" s="12">
+      <c r="E28" s="11">
         <v>715762</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D29" s="10" t="s">
+      <c r="A29" s="10">
+        <v>46170</v>
+      </c>
+      <c r="B29" s="11">
+        <v>-70794</v>
+      </c>
+      <c r="D29" s="10">
+        <v>46169</v>
+      </c>
+      <c r="E29" s="11">
+        <v>396800</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="10">
+        <v>46172</v>
+      </c>
+      <c r="B30" s="11">
+        <v>297815</v>
+      </c>
+      <c r="D30" s="10">
+        <v>46170</v>
+      </c>
+      <c r="E30" s="11">
+        <v>326006</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="12">
-        <v>4753981</v>
+      <c r="B31" s="11">
+        <v>623821</v>
+      </c>
+      <c r="D31" s="10">
+        <v>46172</v>
+      </c>
+      <c r="E31" s="11">
+        <v>623821</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D32" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="11">
+        <v>6100608</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B36" t="s">
@@ -9588,67 +9959,91 @@
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="11">
+      <c r="A37" s="10">
         <v>46154</v>
       </c>
-      <c r="B37" s="12">
+      <c r="B37" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="11">
+      <c r="A38" s="10">
         <v>46155</v>
       </c>
-      <c r="B38" s="12">
+      <c r="B38" s="11">
         <v>502833</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="11">
+      <c r="A39" s="10">
         <v>46157</v>
       </c>
-      <c r="B39" s="12">
+      <c r="B39" s="11">
         <v>683489</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="11">
+      <c r="A40" s="10">
         <v>46158</v>
       </c>
-      <c r="B40" s="12">
+      <c r="B40" s="11">
         <v>993143</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="11">
+      <c r="A41" s="10">
         <v>46163</v>
       </c>
-      <c r="B41" s="12">
+      <c r="B41" s="11">
         <v>1097997</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="11">
+      <c r="A42" s="10">
         <v>46166</v>
       </c>
-      <c r="B42" s="12">
+      <c r="B42" s="11">
         <v>760757</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="11">
+      <c r="A43" s="10">
         <v>46168</v>
       </c>
-      <c r="B43" s="12">
+      <c r="B43" s="11">
         <v>715762</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="10">
+        <v>46169</v>
+      </c>
+      <c r="B44" s="11">
+        <v>396800</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="10">
+        <v>46170</v>
+      </c>
+      <c r="B45" s="11">
+        <v>326006</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="10">
+        <v>46172</v>
+      </c>
+      <c r="B46" s="11">
+        <v>623821</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="12">
-        <v>4753981</v>
+      <c r="B47" s="11">
+        <v>6100608</v>
       </c>
     </row>
   </sheetData>
@@ -9669,7 +10064,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
